--- a/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$59</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2812" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2157" uniqueCount="413">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -586,7 +586,7 @@
 </t>
   </si>
   <si>
-    <t>Service category</t>
+    <t>Type de résultat</t>
   </si>
   <si>
     <t>A code that classifies the clinical discipline, department or diagnostic service that created the report (e.g. cardiology, biochemistry, hematology, MRI). This is used for searching, sorting and display purposes.</t>
@@ -595,13 +595,7 @@
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -620,13 +614,16 @@
 </t>
   </si>
   <si>
-    <t>Type de résultat</t>
+    <t>Code du résultat</t>
   </si>
   <si>
     <t>A code or name that describes this diagnostic report.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-result-type-document</t>
+    <t>Codes that describe Diagnostic Reports.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/report-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -807,7 +804,26 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.id</t>
+    <t>DiagnosticReport.resultsInterpreter</t>
+  </si>
+  <si>
+    <t>Analyzed by
+Reported by</t>
+  </si>
+  <si>
+    <t>Auteur</t>
+  </si>
+  <si>
+    <t>The practitioner or organization that is responsible for the report's conclusions and interpretations.</t>
+  </si>
+  <si>
+    <t>Might not be the same entity that takes responsibility for the clinical report.</t>
+  </si>
+  <si>
+    <t>OBR-32, PRT-8 (where this PRT-4-Participation = "PI")</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -826,7 +842,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension</t>
+    <t>DiagnosticReport.resultsInterpreter.extension</t>
   </si>
   <si>
     <t>Extension</t>
@@ -848,306 +864,157 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension:performerFunction</t>
-  </si>
-  <si>
-    <t>performerFunction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {event-performerFunction}
+    <t>DiagnosticReport.resultsInterpreter.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
 </t>
   </si>
   <si>
-    <t>Type of performance</t>
-  </si>
-  <si>
-    <t>Distinguishes the type of involvement of the performer in the event. For example, 'author',  'verifier' or 'responsible party'.</t>
-  </si>
-  <si>
-    <t>Event.performer.function</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
+    <t>Auteur du compte-rendu (Médecin - Radiologue - Biologiste ...)</t>
+  </si>
+  <si>
+    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor</t>
+  </si>
+  <si>
+    <t>actor</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document)
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/event-performerFunction</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.value[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-function</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.value[x].id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.value[x].extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.value[x].coding</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>PPRF</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:performerFunction.value[x].text</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.reference</t>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.reference</t>
   </si>
   <si>
     <t>Literal reference, Relative, internal or absolute URL</t>
@@ -1166,7 +1033,7 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.type</t>
+    <t>DiagnosticReport.resultsInterpreter.type</t>
   </si>
   <si>
     <t>Type the reference refers to (e.g. "Patient")</t>
@@ -1179,6 +1046,9 @@
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
@@ -1188,7 +1058,7 @@
     <t>Reference.type</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.identifier</t>
+    <t>DiagnosticReport.resultsInterpreter.identifier</t>
   </si>
   <si>
     <t>Logical reference, when literal reference is not known</t>
@@ -1209,7 +1079,7 @@
     <t>.identifier</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.display</t>
+    <t>DiagnosticReport.resultsInterpreter.display</t>
   </si>
   <si>
     <t>Text alternative for the resource</t>
@@ -1222,139 +1092,6 @@
   </si>
   <si>
     <t>Reference.display</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter</t>
-  </si>
-  <si>
-    <t>Analyzed by
-Reported by</t>
-  </si>
-  <si>
-    <t>Auteur</t>
-  </si>
-  <si>
-    <t>The practitioner or organization that is responsible for the report's conclusions and interpretations.</t>
-  </si>
-  <si>
-    <t>Might not be the same entity that takes responsibility for the clinical report.</t>
-  </si>
-  <si>
-    <t>OBR-32, PRT-8 (where this PRT-4-Participation = "PI")</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.value[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.value[x].id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.value[x].extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.value[x].coding</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x].coding</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:performerFunction.value[x].text</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.reference</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.type</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.identifier</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.display</t>
   </si>
   <si>
     <t>DiagnosticReport.specimen</t>
@@ -1386,11 +1123,11 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-observation-result-document)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-observation-result-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-observation-laboratory-report-results-document)
 </t>
   </si>
   <si>
-    <t>Resultat</t>
+    <t>Résultat</t>
   </si>
   <si>
     <t>[Observations](http://hl7.org/fhir/R4/observation.html)  that are part of this diagnostic report.</t>
@@ -1438,7 +1175,7 @@
 </t>
   </si>
   <si>
-    <t>Key images associated with this report</t>
+    <t>Images clés associées à ce rapport</t>
   </si>
   <si>
     <t>A list of key images associated with this report. The images are generally created during the diagnostic process, and may be directly of the patient, or of treated specimens (i.e. slides of interest).</t>
@@ -1454,6 +1191,9 @@
   </si>
   <si>
     <t>DiagnosticReport.media.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>DiagnosticReport.media.modifierExtension</t>
@@ -1494,11 +1234,11 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-media-document)
 </t>
   </si>
   <si>
-    <t>Reference to the image source</t>
+    <t>Lien vers les images clés</t>
   </si>
   <si>
     <t>Reference to the image source.</t>
@@ -1514,7 +1254,7 @@
 </t>
   </si>
   <si>
-    <t>Clinical conclusion (interpretation) of test results</t>
+    <t>Conclusions cliniques et interprétations du rapport.</t>
   </si>
   <si>
     <t>Concise and clinically contextualized summary conclusion (interpretation/impression) of the diagnostic report.</t>
@@ -1536,6 +1276,9 @@
   </si>
   <si>
     <t>One or more codes that represent the summary conclusion (interpretation/impression) of the diagnostic report.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Diagnosis codes provided as adjuncts to the report.</t>
@@ -1554,7 +1297,7 @@
 </t>
   </si>
   <si>
-    <t>Entire report as issued</t>
+    <t>Copie du document</t>
   </si>
   <si>
     <t>Rich text representation of the entire result as issued by the diagnostic service. Multiple formats are allowed but they SHALL be semantically equivalent.</t>
@@ -1883,12 +1626,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN77"/>
+  <dimension ref="A1:AN59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="75.65625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="60.44140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.58203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="67.1484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="53.375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1896,7 +1639,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="234.27734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1911,7 +1654,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.2421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3088,10 +2831,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>91</v>
@@ -3421,7 +3164,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>179</v>
       </c>
@@ -3434,13 +3177,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
@@ -3484,13 +3227,11 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3526,25 +3267,25 @@
         <v>80</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AM14" t="s" s="2">
+    </row>
+    <row r="15" hidden="true">
+      <c r="A15" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AN14" t="s" s="2">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3554,7 +3295,7 @@
         <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>80</v>
@@ -3566,10 +3307,10 @@
         <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3596,11 +3337,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3618,7 +3361,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>90</v>
@@ -3633,28 +3376,28 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>199</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3673,17 +3416,17 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3732,7 +3475,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3747,28 +3490,28 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3787,19 +3530,19 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3848,7 +3591,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3863,28 +3606,28 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3903,19 +3646,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>13</v>
       </c>
       <c r="M18" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3964,7 +3707,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3979,28 +3722,28 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4019,19 +3762,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4080,7 +3823,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4098,25 +3841,25 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>240</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4135,19 +3878,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4196,7 +3939,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4211,56 +3954,60 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AN20" t="s" s="2">
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>251</v>
       </c>
-    </row>
-    <row r="21" hidden="true">
-      <c r="A21" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4308,39 +4055,39 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AM21" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>80</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4348,10 +4095,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>80</v>
@@ -4363,7 +4110,7 @@
         <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>136</v>
+        <v>258</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>259</v>
@@ -4408,40 +4155,40 @@
         <v>80</v>
       </c>
       <c r="AB22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AC22" t="s" s="2">
+      <c r="AG22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
@@ -4449,14 +4196,12 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4465,7 +4210,7 @@
         <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>80</v>
@@ -4477,13 +4222,13 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>267</v>
+        <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4522,19 +4267,19 @@
         <v>80</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4549,7 +4294,7 @@
         <v>141</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
@@ -4563,21 +4308,23 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="B24" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4589,13 +4336,13 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4646,19 +4393,19 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>273</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
@@ -4667,7 +4414,7 @@
         <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>80</v>
@@ -4675,10 +4422,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4689,7 +4436,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
@@ -4701,7 +4448,7 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>136</v>
+        <v>258</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>259</v>
@@ -4746,40 +4493,40 @@
         <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AC25" t="s" s="2">
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>80</v>
@@ -4787,10 +4534,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4798,10 +4545,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>90</v>
+        <v>279</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -4813,24 +4560,22 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>80</v>
@@ -4860,31 +4605,31 @@
         <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
@@ -4893,7 +4638,7 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>80</v>
@@ -4901,12 +4646,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>80</v>
       </c>
@@ -4927,13 +4674,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>181</v>
+        <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4960,11 +4707,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>288</v>
+        <v>80</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -4982,19 +4731,19 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
@@ -5003,7 +4752,7 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -5011,10 +4760,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5037,13 +4786,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5094,7 +4843,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5115,7 +4864,7 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>80</v>
@@ -5123,21 +4872,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
@@ -5152,14 +4901,12 @@
         <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5196,19 +4943,19 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5229,7 +4976,7 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -5237,10 +4984,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5248,10 +4995,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -5260,29 +5007,27 @@
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>298</v>
+        <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>80</v>
+        <v>281</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>80</v>
@@ -5324,28 +5069,28 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>304</v>
+        <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>305</v>
+        <v>133</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5353,10 +5098,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5379,13 +5124,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>253</v>
+        <v>110</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5397,7 +5142,7 @@
         <v>80</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>80</v>
+        <v>296</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>80</v>
@@ -5412,13 +5157,11 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5436,7 +5179,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5448,7 +5191,7 @@
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
@@ -5457,7 +5200,7 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5465,21 +5208,23 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="D32" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>80</v>
@@ -5494,14 +5239,12 @@
         <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>137</v>
+        <v>301</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5538,19 +5281,19 @@
         <v>80</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5571,7 +5314,7 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5579,10 +5322,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5602,23 +5345,19 @@
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>104</v>
+        <v>258</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>259</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
@@ -5666,7 +5405,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>261</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5678,16 +5417,16 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>317</v>
+        <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>318</v>
+        <v>262</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5695,10 +5434,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5709,7 +5448,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5718,20 +5457,18 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>253</v>
+        <v>136</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>264</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5768,40 +5505,40 @@
         <v>80</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>269</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>325</v>
+        <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>326</v>
+        <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5809,10 +5546,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>287</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5820,7 +5557,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>90</v>
@@ -5832,30 +5569,30 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>288</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>332</v>
+        <v>80</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>80</v>
@@ -5894,10 +5631,10 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>291</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>90</v>
@@ -5906,16 +5643,16 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>334</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>335</v>
+        <v>133</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5923,10 +5660,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>293</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5946,21 +5683,19 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>253</v>
+        <v>181</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>294</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>340</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6008,7 +5743,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>341</v>
+        <v>298</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6026,10 +5761,10 @@
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>342</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>343</v>
+        <v>133</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -6037,18 +5772,20 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="D37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>90</v>
@@ -6060,23 +5797,19 @@
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>346</v>
+        <v>136</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>264</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6124,28 +5857,28 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>269</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -6153,10 +5886,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>283</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6176,23 +5909,19 @@
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>259</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6240,7 +5969,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>360</v>
+        <v>261</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6252,16 +5981,16 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>361</v>
+        <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>362</v>
+        <v>262</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -6269,10 +5998,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>285</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6283,7 +6012,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
@@ -6292,20 +6021,18 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>136</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>264</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6342,31 +6069,31 @@
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>367</v>
+        <v>269</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>368</v>
+        <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6375,7 +6102,7 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
@@ -6383,10 +6110,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>369</v>
+        <v>310</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>369</v>
+        <v>287</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6394,7 +6121,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>90</v>
@@ -6406,19 +6133,19 @@
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>370</v>
+        <v>288</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>371</v>
+        <v>289</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>372</v>
+        <v>290</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6426,7 +6153,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>80</v>
+        <v>307</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>80</v>
@@ -6444,13 +6171,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>287</v>
+        <v>80</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>373</v>
+        <v>80</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -6468,10 +6195,10 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>375</v>
+        <v>291</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>90</v>
@@ -6480,7 +6207,7 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6497,10 +6224,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>376</v>
+        <v>311</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>376</v>
+        <v>293</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6520,20 +6247,18 @@
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>149</v>
+        <v>312</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>377</v>
+        <v>294</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6582,7 +6307,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>380</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6603,7 +6328,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>381</v>
+        <v>133</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -6611,10 +6336,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>314</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6622,7 +6347,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>90</v>
@@ -6634,19 +6359,19 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>383</v>
+        <v>288</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>384</v>
+        <v>289</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>385</v>
+        <v>290</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6654,7 +6379,7 @@
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>80</v>
+        <v>315</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>80</v>
@@ -6696,10 +6421,10 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>386</v>
+        <v>291</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>90</v>
@@ -6708,7 +6433,7 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -6723,48 +6448,44 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>387</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>387</v>
+        <v>317</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>388</v>
+        <v>80</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>243</v>
+        <v>318</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>389</v>
+        <v>294</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6812,13 +6533,13 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>387</v>
+        <v>298</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
@@ -6827,24 +6548,24 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>392</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>250</v>
+        <v>133</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>319</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>319</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6864,18 +6585,20 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>254</v>
+        <v>320</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -6924,7 +6647,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>256</v>
+        <v>323</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6933,10 +6656,10 @@
         <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
@@ -6945,7 +6668,7 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
@@ -6953,10 +6676,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>394</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>394</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6964,10 +6687,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -6976,18 +6699,20 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7012,43 +6737,43 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>80</v>
+        <v>329</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>264</v>
+        <v>332</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7057,7 +6782,7 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
@@ -7065,20 +6790,18 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>395</v>
+        <v>333</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>90</v>
@@ -7090,18 +6813,20 @@
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>267</v>
+        <v>149</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>268</v>
+        <v>334</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7150,28 +6875,28 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>264</v>
+        <v>337</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>80</v>
+        <v>338</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7179,10 +6904,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>339</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>397</v>
+        <v>339</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7202,18 +6927,20 @@
         <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>254</v>
+        <v>340</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7262,7 +6989,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>256</v>
+        <v>343</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7271,10 +6998,10 @@
         <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>273</v>
+        <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7283,7 +7010,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7291,10 +7018,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>398</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>399</v>
+        <v>344</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7305,7 +7032,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
@@ -7317,16 +7044,20 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>136</v>
+        <v>345</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>259</v>
+        <v>346</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7362,19 +7093,19 @@
         <v>80</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>264</v>
+        <v>344</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7386,41 +7117,41 @@
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>400</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>401</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>80</v>
@@ -7429,24 +7160,26 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>104</v>
+        <v>353</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>278</v>
+        <v>354</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>279</v>
+        <v>355</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>80</v>
@@ -7488,28 +7221,28 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>282</v>
+        <v>351</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>80</v>
+        <v>358</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>133</v>
+        <v>359</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -7517,10 +7250,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>360</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>403</v>
+        <v>360</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7528,10 +7261,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
@@ -7543,15 +7276,17 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>181</v>
+        <v>361</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>285</v>
+        <v>362</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7576,11 +7311,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>288</v>
+        <v>80</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -7598,16 +7335,16 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>289</v>
+        <v>360</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>102</v>
@@ -7619,50 +7356,52 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>133</v>
+        <v>365</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>405</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>80</v>
+        <v>367</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>253</v>
+        <v>368</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>254</v>
+        <v>369</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>255</v>
+        <v>370</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -7710,28 +7449,28 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>256</v>
+        <v>366</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>80</v>
+        <v>372</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>257</v>
+        <v>359</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -7739,21 +7478,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>406</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -7765,17 +7504,15 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>136</v>
+        <v>258</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>137</v>
+        <v>259</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7812,40 +7549,40 @@
         <v>80</v>
       </c>
       <c r="AB52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AC52" t="s" s="2">
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -7853,14 +7590,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>409</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7876,23 +7613,21 @@
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>298</v>
+        <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>299</v>
+        <v>137</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -7940,7 +7675,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7952,16 +7687,16 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>304</v>
+        <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -7969,42 +7704,46 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>411</v>
+        <v>376</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>80</v>
+        <v>377</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>253</v>
+        <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>254</v>
+        <v>378</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8052,19 +7791,19 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>256</v>
+        <v>380</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8073,7 +7812,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8081,21 +7820,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>80</v>
@@ -8107,18 +7846,20 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>136</v>
+        <v>258</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>137</v>
+        <v>382</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>295</v>
+        <v>383</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8154,31 +7895,31 @@
         <v>80</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>264</v>
+        <v>381</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
@@ -8187,18 +7928,18 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>257</v>
+        <v>386</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>415</v>
+        <v>387</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8206,13 +7947,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>80</v>
@@ -8221,20 +7962,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>104</v>
+        <v>388</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>312</v>
+        <v>389</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8282,10 +8019,10 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>316</v>
+        <v>387</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>90</v>
@@ -8300,25 +8037,25 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>317</v>
+        <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>318</v>
+        <v>391</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>80</v>
+        <v>393</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8328,27 +8065,27 @@
         <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>321</v>
+        <v>394</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8396,7 +8133,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>324</v>
+        <v>392</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8414,10 +8151,10 @@
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>325</v>
+        <v>397</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>326</v>
+        <v>398</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -8425,10 +8162,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8439,7 +8176,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
@@ -8448,21 +8185,19 @@
         <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>110</v>
+        <v>181</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>329</v>
+        <v>400</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>330</v>
+        <v>401</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>331</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8471,7 +8206,7 @@
         <v>80</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>80</v>
@@ -8486,13 +8221,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>80</v>
+        <v>402</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>80</v>
+        <v>403</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>80</v>
+        <v>404</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8510,13 +8245,13 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>333</v>
+        <v>399</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
@@ -8528,21 +8263,21 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>335</v>
+        <v>405</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8550,32 +8285,34 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>253</v>
+        <v>407</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>338</v>
+        <v>408</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>340</v>
+        <v>411</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8624,13 +8361,13 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>341</v>
+        <v>406</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
@@ -8642,2077 +8379,17 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>342</v>
+        <v>397</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>343</v>
+        <v>412</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="P73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AN77" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN77">
+  <autoFilter ref="A1:AN59">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10722,7 +8399,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI76">
+  <conditionalFormatting sqref="A2:AI58">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
